--- a/artfynd/A 46552-2022 artfynd.xlsx
+++ b/artfynd/A 46552-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46552-2022 artfynd.xlsx
+++ b/artfynd/A 46552-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>104580296</v>
       </c>
       <c r="B2" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572479.4831739489</v>
+        <v>572479</v>
       </c>
       <c r="R2" t="n">
-        <v>6429588.710675167</v>
+        <v>6429589</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -802,16 +797,11 @@
         <v>104585977</v>
       </c>
       <c r="B3" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -855,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572517.5766008073</v>
+        <v>572518</v>
       </c>
       <c r="R3" t="n">
-        <v>6429655.131346656</v>
+        <v>6429655</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,19 +878,9 @@
           <t>2022-11-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-11-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
